--- a/apps/web/public/import-templates/players-template.xlsx
+++ b/apps/web/public/import-templates/players-template.xlsx
@@ -6,8 +6,8 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="jugadores" sheetId="1" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -17,7 +17,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
-    <t>Nombre completo*</t>
+    <t>Nombre*</t>
+  </si>
+  <si>
+    <t>Apellidos</t>
   </si>
   <si>
     <t>Fecha de nacimiento*</t>
@@ -29,7 +32,10 @@
     <t>Email*</t>
   </si>
   <si>
-    <t>Pepe Gómez García</t>
+    <t>Pepe</t>
+  </si>
+  <si>
+    <t>Gómez García</t>
   </si>
   <si>
     <t>15/03/2010</t>
@@ -41,7 +47,10 @@
     <t>pepe.gomez@example.com</t>
   </si>
   <si>
-    <t>Lucía Sánchez López</t>
+    <t>Lucía</t>
+  </si>
+  <si>
+    <t>Sánchez López</t>
   </si>
   <si>
     <t>03/09/2011</t>
@@ -53,7 +62,10 @@
     <t>familia.lucia@example.com</t>
   </si>
   <si>
-    <t>Mario Ruiz</t>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>Ruiz</t>
   </si>
   <si>
     <t>20/01/2012</t>
@@ -68,10 +80,13 @@
     <t>Cómo rellenarla</t>
   </si>
   <si>
-    <t>Nombre completo</t>
-  </si>
-  <si>
-    <t>Obligatorio. Nombre y apellidos del jugador en una sola celda (ej. "Pepe Gómez García").</t>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Obligatorio. SOLO el nombre del jugador (ej. "Pepe"). Los apellidos van en su propia columna.</t>
+  </si>
+  <si>
+    <t>Opcional. Los apellidos, en su columna (ej. "Gómez García"). Déjala vacía si el jugador solo tiene nombre.</t>
   </si>
   <si>
     <t>Fecha de nacimiento</t>
@@ -171,53 +186,65 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -229,42 +256,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
